--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-06-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5704B9FA-9DE4-4B3A-BA4D-4FCA896642FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7078AA-06DA-4E7F-AC0E-53D1D7903867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34350" yWindow="1410" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="1665" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
